--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>34종 — 예정 20 · 완료 9 · 진행 2 · 템플릿 3</t>
+          <t>34종 — 예정 19 · 완료 10 · 진행 2 · 템플릿 3</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 개발 표준 정의서·권한 정의서 (P1 착수 전) ② 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ③ WBS 내용화</t>
+          <t>① 개발 표준 정의서 (P1 착수 전) ② 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ③ WBS 내용화</t>
         </is>
       </c>
     </row>
@@ -1439,24 +1439,24 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_권한승인정의서.xlsx</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>권한 매트릭스(역할×메뉴 97)·승인 상태기계</t>
+          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>39컴포넌트·API 68·구축 상태 반영</t>
+          <t>39컴포넌트·API 80·구축 상태 반영</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>46테이블 — v0.2: 보완노트 후보 7테이블·물리 설계</t>
+          <t>50테이블 435컬럼 — 보완노트 반영, duct_*는 범위 확정 후</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>34종 — 예정 19 · 완료 10 · 진행 2 · 템플릿 3</t>
+          <t>34종 — 예정 18 · 완료 11 · 진행 2 · 템플릿 3</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 개발 표준 정의서 (P1 착수 전) ② 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ③ WBS 내용화</t>
+          <t>① 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ② WBS 내용화 ③ FVT 내용화</t>
         </is>
       </c>
     </row>
@@ -1476,27 +1476,27 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_개발표준정의서.md</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>코딩·명명·Git·리뷰·API 규약 — P1 착수 전</t>
+          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>39컴포넌트·API 80·구축 상태 반영</t>
+          <t>39컴포넌트·API 95·구축 상태 반영</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>50테이블 435컬럼 — 보완노트 반영, duct_*는 범위 확정 후</t>
+          <t>53테이블 451컬럼 — v0.3 설계 품질 리뷰(정규화·i18n·제약) 반영</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>39컴포넌트·API 95·구축 상태 반영</t>
+          <t>39컴포넌트·API 106·구축 상태 반영</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>53테이블 451컬럼 — v0.3 설계 품질 리뷰(정규화·i18n·제약) 반영</t>
+          <t>53테이블 455컬럼 — v0.4 런타임 경로 리뷰까지 반영</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -606,7 +606,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>34종 — 예정 18 · 완료 11 · 진행 2 · 템플릿 3</t>
+          <t>35종 — 예정 18 · 완료 12 · 진행 2 · 템플릿 3</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1351,32 +1351,32 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>클래스 정의서</t>
+          <t>DB DDL·검증 스크립트</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.4.1</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/ddl/edim_schema.sql · verify_runtime.sql</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>도메인 모델 (개요 §14) — 백엔드 언어 확정 후</t>
+          <t>실 PG16 적용·BOM 재귀/제약 검증 통과 — 마이그레이션 도구 도입 시 초기본</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>인터페이스 정의서</t>
+          <t>클래스 정의서</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>API 상세 스펙(요청/응답/오류)·외부 연계 8종(REQ-I)</t>
+          <t>도메인 모델 (개요 §14) — 백엔드 언어 확정 후</t>
         </is>
       </c>
     </row>
@@ -1431,32 +1431,32 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>권한·승인 정의서</t>
+          <t>인터페이스 정의서</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_권한승인정의서.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
+          <t>API 상세 스펙(요청/응답/오류)·외부 연계 8종(REQ-I)</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>개발 표준 정의서</t>
+          <t>권한·승인 정의서</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_개발표준정의서.md</t>
+          <t>docs/EDIM_권한승인정의서.xlsx</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
+          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
         </is>
       </c>
     </row>
@@ -1511,32 +1511,32 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>공통코드 정의서</t>
+          <t>개발 표준 정의서</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>진행</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>DB정의서 §10 포함</t>
+          <t>docs/EDIM_개발표준정의서.md</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>분리 여부 협의 — 코드 16그룹</t>
+          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>배치(Job) 정의서</t>
+          <t>공통코드 정의서</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DB정의서 §10 포함</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
+          <t>분리 여부 협의 — 코드 16그룹</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>보고서·양식 정의서</t>
+          <t>배치(Job) 정의서</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
+          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
         </is>
       </c>
     </row>
@@ -1624,14 +1624,14 @@
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>구현·시험</t>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>설계</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>단위테스트 계획·결과</t>
+          <t>보고서·양식 정의서</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>P1 개발과 병행</t>
+          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1671,12 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>통합테스트 시나리오</t>
+          <t>단위테스트 계획·결과</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
+          <t>P1 개발과 병행</t>
         </is>
       </c>
     </row>
@@ -1711,17 +1711,17 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>기능확인서 (FVT)</t>
+          <t>통합테스트 시나리오</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>HTML/Excel</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>템플릿</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -1731,12 +1731,12 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>docs/03_기능확인서_FVT/FVT.html</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>기능정의서 178건 → 확인 항목 생성 가능</t>
+          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
         </is>
       </c>
     </row>
@@ -1751,17 +1751,17 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>성능시험 계획·결과</t>
+          <t>기능확인서 (FVT)</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>HTML/Excel</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>템플릿</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/03_기능확인서_FVT/FVT.html</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
+          <t>기능정의서 178건 → 확인 항목 생성 가능</t>
         </is>
       </c>
     </row>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>결함관리대장</t>
+          <t>성능시험 계획·결과</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>시험 단계 운영</t>
+          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
         </is>
       </c>
     </row>
@@ -1824,19 +1824,19 @@
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>이행·운영</t>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>구현·시험</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>데이터 이행 계획서</t>
+          <t>결함관리대장</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>★중요 — 고객 기존 도면·코드·단가·BOM 이관 + AI 학습(RAW DB) 연계</t>
+          <t>시험 단계 운영</t>
         </is>
       </c>
     </row>
@@ -1871,17 +1871,17 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>설치·배포 매뉴얼</t>
+          <t>데이터 이행 계획서</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>진행</t>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
+          <t>★중요 — 고객 기존 도면·코드·단가·BOM 이관 + AI 학습(RAW DB) 연계</t>
         </is>
       </c>
     </row>
@@ -1911,17 +1911,17 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>운영자 매뉴얼</t>
+          <t>설치·배포 매뉴얼</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>백업·모니터링·테넌트 관리·장애 대응</t>
+          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>사용자 매뉴얼</t>
+          <t>운영자 매뉴얼</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
+          <t>백업·모니터링·테넌트 관리·장애 대응</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>교육 계획·자료</t>
+          <t>사용자 매뉴얼</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
         </is>
       </c>
     </row>
@@ -2031,37 +2031,77 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
+          <t>교육 계획·자료</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>이행·운영</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
           <t>검수·인수 문서</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>FVT 승인 연계</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H35"/>
+  <autoFilter ref="A1:H36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -84,12 +84,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FD"/>
+        <fgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00E8F4FD"/>
       </patternFill>
     </fill>
     <fill>
@@ -606,7 +606,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>35종 — 예정 18 · 완료 12 · 진행 2 · 템플릿 3</t>
+          <t>35종 — 예정 18 · 완료 13 · 진행 2 · 템플릿 2</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ② WBS 내용화 ③ FVT 내용화</t>
+          <t>① 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ② FVT 내용화 ③ 인터페이스·클래스 정의서</t>
         </is>
       </c>
     </row>
@@ -836,27 +836,27 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>HTML/Excel</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>템플릿</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>docs/04_WBS/WBS.html</t>
+          <t>docs/04_WBS/EDIM_WBS.xlsx</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Phase 계획(P1~P5) 기반 내용화 필요</t>
+          <t>38 Task·44주 간트·M1~M4 — 시작일 가정, 계약 시 재산정</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -959,7 +959,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -984,7 +984,7 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -999,7 +999,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1024,7 +1024,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1039,7 +1039,7 @@
           <t>Excel(자동)</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1064,7 +1064,7 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1079,7 +1079,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1104,7 +1104,7 @@
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1119,7 +1119,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1144,7 +1144,7 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1159,7 +1159,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1184,7 +1184,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1239,7 +1239,7 @@
           <t>MD+Excel</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1279,7 +1279,7 @@
           <t>MD+Excel</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1319,7 +1319,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1359,7 +1359,7 @@
           <t>SQL</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1479,7 +1479,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1519,7 +1519,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>완료</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -654,8 +654,9 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -691,10 +692,15 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>작업자</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>파일/위치</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>비고·선행조건</t>
         </is>
@@ -729,12 +735,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>docs/01_제안서/PROPOSAL.html</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>사업 조건(범위·금액·일정) 확정 후 작성</t>
         </is>
@@ -769,12 +780,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>제안 확정 후</t>
         </is>
@@ -809,12 +825,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>착수 시 — 범위·조직·일정·보고 체계</t>
         </is>
@@ -849,12 +870,17 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>docs/04_WBS/EDIM_WBS.xlsx</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>38 Task·44주 간트·M1~M4 — 시작일 가정, 계약 시 재산정</t>
         </is>
@@ -889,12 +915,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>미결정사항(DB정의서 §12 등)이 초기 위험 항목</t>
         </is>
@@ -929,12 +960,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>Management Grade·개인정보·서버 보안 포함</t>
         </is>
@@ -969,12 +1005,17 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_개요.md</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>발표자료 78슬라이드 분석 — 기준 문서</t>
         </is>
@@ -1009,12 +1050,17 @@
           <t>v0.2</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>docs/02_요구사항/EDIM_요구사항정의서.xlsx</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>기능 50·비기능 22·인터페이스 8</t>
         </is>
@@ -1049,12 +1095,17 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_요구사항추적표.xlsx</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>REQ→기능→메뉴→화면→컴포넌트→DB, 커버리지 178/178</t>
         </is>
@@ -1089,12 +1140,17 @@
           <t>v0.2</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_기능정의서.xlsx</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>14모듈 178기능 — v0.3 보강 예정(Constant·AR 등)</t>
         </is>
@@ -1129,12 +1185,17 @@
           <t>v0.3</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_메뉴정의서.xlsx</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>97메뉴, PPT 3차 전수 대조</t>
         </is>
@@ -1169,12 +1230,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_요구사항_보완노트.md</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>재검토 근거·협의 필요 4건</t>
         </is>
@@ -1209,12 +1275,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>고객사 확정 후 — 기존 업무·시스템·데이터 조사</t>
         </is>
@@ -1249,12 +1320,17 @@
           <t>v0.2</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_컴포넌트_정의서.md / EDIM_컴포넌트정의서.xlsx</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>39컴포넌트·API 106·구축 상태 반영</t>
         </is>
@@ -1289,12 +1365,17 @@
           <t>v0.2</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_DB_정의서.md / EDIM_DB정의서.xlsx</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>53테이블 455컬럼 — v0.4 런타임 경로 리뷰까지 반영</t>
         </is>
@@ -1329,12 +1410,17 @@
           <t>v0.2</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_화면설계서.html · https://edim.seekerslab.com/design/</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>16화면 — 상세 설계 시 전 화면 확장</t>
         </is>
@@ -1369,12 +1455,17 @@
           <t>v0.4.1</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>docs/ddl/edim_schema.sql · verify_runtime.sql</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>실 PG16 적용·BOM 재귀/제약 검증 통과 — 마이그레이션 도구 도입 시 초기본</t>
         </is>
@@ -1409,12 +1500,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>도메인 모델 (개요 §14) — 백엔드 언어 확정 후</t>
         </is>
@@ -1449,12 +1545,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>API 상세 스펙(요청/응답/오류)·외부 연계 8종(REQ-I)</t>
         </is>
@@ -1489,12 +1590,17 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_권한승인정의서.xlsx</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
         </is>
@@ -1529,12 +1635,17 @@
           <t>v0.1</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>docs/EDIM_개발표준정의서.md</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
         </is>
@@ -1569,12 +1680,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>DB정의서 §10 포함</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>분리 여부 협의 — 코드 16그룹</t>
         </is>
@@ -1609,12 +1725,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
         </is>
@@ -1649,12 +1770,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
         </is>
@@ -1689,12 +1815,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>P1 개발과 병행</t>
         </is>
@@ -1729,12 +1860,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
         </is>
@@ -1769,12 +1905,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>docs/03_기능확인서_FVT/FVT.html</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>기능정의서 178건 → 확인 항목 생성 가능</t>
         </is>
@@ -1809,12 +1950,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
         </is>
@@ -1849,12 +1995,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>시험 단계 운영</t>
         </is>
@@ -1889,12 +2040,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>★중요 — 고객 기존 도면·코드·단가·BOM 이관 + AI 학습(RAW DB) 연계</t>
         </is>
@@ -1929,12 +2085,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
         </is>
@@ -1969,12 +2130,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>백업·모니터링·테넌트 관리·장애 대응</t>
         </is>
@@ -2009,12 +2175,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
         </is>
@@ -2049,12 +2220,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
         </is>
@@ -2089,12 +2265,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>FVT 승인 연계</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -50,7 +50,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -65,11 +65,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEFC2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3ECF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -139,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,9 +173,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -606,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>35종 — 예정 18 · 완료 13 · 진행 2 · 템플릿 2</t>
+          <t>35종 — 예정 18 · 완료 15 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -630,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 데이터 이행 계획서 (AI 학습과 연계, 조기 협의) ② FVT 내용화 ③ 인터페이스·클래스 정의서</t>
+          <t>① 인터페이스 정의서 (OpenAPI) ② 클래스 정의서 ③ 착수 문서(수행계획·위험대장·보안계획)</t>
         </is>
       </c>
     </row>
@@ -727,7 +719,7 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>템플릿</t>
+          <t>예정</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -742,12 +734,12 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>docs/01_제안서/PROPOSAL.html</t>
+          <t>_template/01_제안서 (필요 시 복사)</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>사업 조건(범위·금액·일정) 확정 후 작성</t>
+          <t>사업 조건 확정 후 작성 — 중복 템플릿은 정리(2026-07-07)</t>
         </is>
       </c>
     </row>
@@ -770,7 +762,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -800,7 +792,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>착수</t>
         </is>
@@ -815,7 +807,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -845,7 +837,7 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>착수</t>
         </is>
@@ -860,7 +852,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -890,7 +882,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>착수</t>
         </is>
@@ -905,7 +897,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -935,7 +927,7 @@
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>착수</t>
         </is>
@@ -950,7 +942,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -980,7 +972,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -995,7 +987,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1025,7 +1017,7 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1040,7 +1032,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1070,7 +1062,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1085,7 +1077,7 @@
           <t>Excel(자동)</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1115,7 +1107,7 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1130,7 +1122,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1160,7 +1152,7 @@
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1175,7 +1167,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1205,7 +1197,7 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1220,7 +1212,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1250,7 +1242,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>분석</t>
         </is>
@@ -1265,7 +1257,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1295,7 +1287,7 @@
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1310,7 +1302,7 @@
           <t>MD+Excel</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1340,7 +1332,7 @@
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1355,7 +1347,7 @@
           <t>MD+Excel</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1385,7 +1377,7 @@
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1400,7 +1392,7 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1430,7 +1422,7 @@
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1445,7 +1437,7 @@
           <t>SQL</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1475,7 +1467,7 @@
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1490,7 +1482,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1520,7 +1512,7 @@
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1535,7 +1527,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1565,7 +1557,7 @@
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1580,7 +1572,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1610,7 +1602,7 @@
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1625,7 +1617,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
@@ -1655,7 +1647,7 @@
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1670,7 +1662,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
@@ -1700,7 +1692,7 @@
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1715,7 +1707,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1745,7 +1737,7 @@
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>설계</t>
         </is>
@@ -1760,7 +1752,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1790,7 +1782,7 @@
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>구현·시험</t>
         </is>
@@ -1805,7 +1797,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1835,7 +1827,7 @@
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>구현·시험</t>
         </is>
@@ -1850,7 +1842,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1880,7 +1872,7 @@
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>구현·시험</t>
         </is>
@@ -1892,17 +1884,17 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>HTML/Excel</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>템플릿</t>
+          <t>Excel(자동)</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1912,12 +1904,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>docs/03_기능확인서_FVT/FVT.html</t>
+          <t>docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>기능정의서 178건 → 확인 항목 생성 가능</t>
+          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1917,7 @@
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>구현·시험</t>
         </is>
@@ -1940,7 +1932,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -1970,7 +1962,7 @@
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>구현·시험</t>
         </is>
@@ -1985,7 +1977,7 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -2015,7 +2007,7 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2027,17 +2019,17 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2047,12 +2039,12 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_데이터이행계획서.md</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>★중요 — 고객 기존 도면·코드·단가·BOM 이관 + AI 학습(RAW DB) 연계</t>
+          <t>9대상·5단계·검증 6기준 — 조사(2.3) 후 v0.2 갱신</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2052,7 @@
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2075,7 +2067,7 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>진행</t>
         </is>
@@ -2105,7 +2097,7 @@
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2120,7 +2112,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -2150,7 +2142,7 @@
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2165,7 +2157,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -2195,7 +2187,7 @@
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2210,7 +2202,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
@@ -2240,7 +2232,7 @@
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>이행·운영</t>
         </is>
@@ -2255,7 +2247,7 @@
           <t>문서</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>35종 — 예정 18 · 완료 15 · 진행 2</t>
+          <t>35종 — 예정 17 · 완료 16 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 인터페이스 정의서 (OpenAPI) ② 클래스 정의서 ③ 착수 문서(수행계획·위험대장·보안계획)</t>
+          <t>① 클래스 정의서 ② 착수 문서(수행계획·위험대장·보안계획) ③ 배치·보고서양식 정의서</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD+YAML</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_인터페이스정의서.md · docs/api/edim-openapi.yaml</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>API 상세 스펙(요청/응답/오류)·외부 연계 8종(REQ-I)</t>
+          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>35종 — 예정 17 · 완료 16 · 진행 2</t>
+          <t>35종 — 예정 16 · 완료 17 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 클래스 정의서 ② 착수 문서(수행계획·위험대장·보안계획) ③ 배치·보고서양식 정의서</t>
+          <t>① 착수 문서(수행계획·위험대장·보안계획) ② 배치·보고서양식 정의서 ③ 운영·사용자 매뉴얼(안정화 단계)</t>
         </is>
       </c>
     </row>
@@ -1479,17 +1479,17 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_클래스정의서.md</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>도메인 모델 (개요 §14) — 백엔드 언어 확정 후</t>
+          <t>언어 중립 — 11도메인·Aggregate 22·인바리언트↔DB제약 대응표</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1399,7 +1399,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>v0.2</t>
+          <t>v0.3</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>16화면 — 상세 설계 시 전 화면 확장</t>
+          <t>24화면 — 메뉴 미배정 주요 화면 보완(v0.3)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>35종 — 예정 16 · 완료 17 · 진행 2</t>
+          <t>36종 — 예정 16 · 완료 18 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>클래스 정의서</t>
+          <t>디자인 시안 (Hi-Fi)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_클래스정의서.md</t>
+          <t>docs/EDIM_디자인시안.html · https://edim.seekerslab.com/design/hifi/</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>언어 중립 — 11도메인·Aggregate 22·인바리언트↔DB제약 대응표</t>
+          <t>디자인 시스템(토큰)+핵심 6페이지 — 개발 시 CSS 변수 이식</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>인터페이스 정의서</t>
+          <t>클래스 정의서</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>MD+YAML</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_인터페이스정의서.md · docs/api/edim-openapi.yaml</t>
+          <t>docs/EDIM_클래스정의서.md</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
+          <t>언어 중립 — 11도메인·Aggregate 22·인바리언트↔DB제약 대응표</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>권한·승인 정의서</t>
+          <t>인터페이스 정의서</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>MD+YAML</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_권한승인정의서.xlsx</t>
+          <t>docs/EDIM_인터페이스정의서.md · docs/api/edim-openapi.yaml</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
+          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>개발 표준 정의서</t>
+          <t>권한·승인 정의서</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_개발표준정의서.md</t>
+          <t>docs/EDIM_권한승인정의서.xlsx</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
+          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
         </is>
       </c>
     </row>
@@ -1654,22 +1654,22 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>공통코드 정의서</t>
+          <t>개발 표준 정의서</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>진행</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>DB정의서 §10 포함</t>
+          <t>docs/EDIM_개발표준정의서.md</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>분리 여부 협의 — 코드 16그룹</t>
+          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
         </is>
       </c>
     </row>
@@ -1699,17 +1699,17 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>배치(Job) 정의서</t>
+          <t>공통코드 정의서</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DB정의서 §10 포함</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
+          <t>분리 여부 협의 — 코드 16그룹</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>보고서·양식 정의서</t>
+          <t>배치(Job) 정의서</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
+          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
         </is>
       </c>
     </row>
@@ -1782,14 +1782,14 @@
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>구현·시험</t>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>설계</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>단위테스트 계획·결과</t>
+          <t>보고서·양식 정의서</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>P1 개발과 병행</t>
+          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
         </is>
       </c>
     </row>
@@ -1834,12 +1834,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>통합테스트 시나리오</t>
+          <t>단위테스트 계획·결과</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
+          <t>P1 개발과 병행</t>
         </is>
       </c>
     </row>
@@ -1879,22 +1879,22 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>기능확인서 (FVT)</t>
+          <t>통합테스트 시나리오</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Excel(자동)</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
+          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>성능시험 계획·결과</t>
+          <t>기능확인서 (FVT)</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>Excel(자동)</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
+          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
         </is>
       </c>
     </row>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>결함관리대장</t>
+          <t>성능시험 계획·결과</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>시험 단계 운영</t>
+          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
         </is>
       </c>
     </row>
@@ -2007,29 +2007,29 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>이행·운영</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>구현·시험</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>데이터 이행 계획서</t>
+          <t>결함관리대장</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_데이터이행계획서.md</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>9대상·5단계·검증 6기준 — 조사(2.3) 후 v0.2 갱신</t>
+          <t>시험 단계 운영</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>설치·배포 매뉴얼</t>
+          <t>데이터 이행 계획서</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2067,14 +2067,14 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>진행</t>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
+          <t>docs/EDIM_데이터이행계획서.md</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
+          <t>9대상·5단계·검증 6기준 — 조사(2.3) 후 v0.2 갱신</t>
         </is>
       </c>
     </row>
@@ -2104,17 +2104,17 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>운영자 매뉴얼</t>
+          <t>설치·배포 매뉴얼</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>백업·모니터링·테넌트 관리·장애 대응</t>
+          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>사용자 매뉴얼</t>
+          <t>운영자 매뉴얼</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
+          <t>백업·모니터링·테넌트 관리·장애 대응</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>교육 계획·자료</t>
+          <t>사용자 매뉴얼</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
         </is>
       </c>
     </row>
@@ -2239,42 +2239,87 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
+          <t>교육 계획·자료</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>이행·운영</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
           <t>검수·인수 문서</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>FVT 승인 연계</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H36"/>
+  <autoFilter ref="A1:H37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="산출물목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'산출물목록'!$A$1:$H$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>36종 — 예정 16 · 완료 18 · 진행 2</t>
+          <t>37종 — 예정 16 · 완료 19 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>디자인 시안 (Hi-Fi)</t>
+          <t>디자인 시안 A (Modern)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_디자인시안.html · https://edim.seekerslab.com/design/hifi/</t>
+          <t>docs/EDIM_디자인시안.html · /design/hifi/</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>디자인 시스템(토큰)+핵심 6페이지 — 개발 시 CSS 변수 이식</t>
+          <t>브랜드 접점용(로그인·Dashboard·모바일) — B-06 권고 참조</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1519,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>클래스 정의서</t>
+          <t>디자인 시안 B (Dense) ★권고</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_클래스정의서.md</t>
+          <t>docs/EDIM_디자인시안_B_dense.html · /design/dense/</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>언어 중립 — 11도메인·Aggregate 22·인바리언트↔DB제약 대응표</t>
+          <t>레거시 패턴 조사(SAP·더존·CAD·Excel)+22px 컨트롤+MDI·F-key — 업무 화면 표준</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>인터페이스 정의서</t>
+          <t>클래스 정의서</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>MD+YAML</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_인터페이스정의서.md · docs/api/edim-openapi.yaml</t>
+          <t>docs/EDIM_클래스정의서.md</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
+          <t>언어 중립 — 11도메인·Aggregate 22·인바리언트↔DB제약 대응표</t>
         </is>
       </c>
     </row>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>권한·승인 정의서</t>
+          <t>인터페이스 정의서</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>MD+YAML</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1634,12 +1634,12 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_권한승인정의서.xlsx</t>
+          <t>docs/EDIM_인터페이스정의서.md · docs/api/edim-openapi.yaml</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
+          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1654,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>개발 표준 정의서</t>
+          <t>권한·승인 정의서</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_개발표준정의서.md</t>
+          <t>docs/EDIM_권한승인정의서.xlsx</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
+          <t>매트릭스 97메뉴 자동 도출·승인 흐름 13·Platform 범위 8·Grade</t>
         </is>
       </c>
     </row>
@@ -1699,22 +1699,22 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>공통코드 정의서</t>
+          <t>개발 표준 정의서</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>진행</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>DB정의서 §10 포함</t>
+          <t>docs/EDIM_개발표준정의서.md</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>분리 여부 협의 — 코드 16그룹</t>
+          <t>언어중립 핵심+FastAPI·React/TS 기준, 개정 트리거 5건 명시</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>배치(Job) 정의서</t>
+          <t>공통코드 정의서</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DB정의서 §10 포함</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
+          <t>분리 여부 협의 — 코드 16그룹</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>보고서·양식 정의서</t>
+          <t>배치(Job) 정의서</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
+          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
         </is>
       </c>
     </row>
@@ -1827,14 +1827,14 @@
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>구현·시험</t>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>설계</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>단위테스트 계획·결과</t>
+          <t>보고서·양식 정의서</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>P1 개발과 병행</t>
+          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>통합테스트 시나리오</t>
+          <t>단위테스트 계획·결과</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
+          <t>P1 개발과 병행</t>
         </is>
       </c>
     </row>
@@ -1924,22 +1924,22 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>기능확인서 (FVT)</t>
+          <t>통합테스트 시나리오</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Excel(자동)</t>
-        </is>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
+          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
         </is>
       </c>
     </row>
@@ -1969,22 +1969,22 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>성능시험 계획·결과</t>
+          <t>기능확인서 (FVT)</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>Excel(자동)</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/03_기능확인서_FVT/EDIM_기능확인서.xlsx</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
+          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
         </is>
       </c>
     </row>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>결함관리대장</t>
+          <t>성능시험 계획·결과</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>문서</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>시험 단계 운영</t>
+          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
         </is>
       </c>
     </row>
@@ -2052,29 +2052,29 @@
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>이행·운영</t>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>구현·시험</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>데이터 이행 계획서</t>
+          <t>결함관리대장</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>MD</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>완료</t>
+          <t>Excel</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_데이터이행계획서.md</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>9대상·5단계·검증 6기준 — 조사(2.3) 후 v0.2 갱신</t>
+          <t>시험 단계 운영</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>설치·배포 매뉴얼</t>
+          <t>데이터 이행 계획서</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2112,14 +2112,14 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>진행</t>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
+          <t>docs/EDIM_데이터이행계획서.md</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
+          <t>9대상·5단계·검증 6기준 — 조사(2.3) 후 v0.2 갱신</t>
         </is>
       </c>
     </row>
@@ -2149,17 +2149,17 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>운영자 매뉴얼</t>
+          <t>설치·배포 매뉴얼</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>진행</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>백업·모니터링·테넌트 관리·장애 대응</t>
+          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>사용자 매뉴얼</t>
+          <t>운영자 매뉴얼</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
+          <t>백업·모니터링·테넌트 관리·장애 대응</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>교육 계획·자료</t>
+          <t>사용자 매뉴얼</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
         </is>
       </c>
     </row>
@@ -2284,42 +2284,87 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
+          <t>교육 계획·자료</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>문서</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>Set-up 사용자(코드·Macro 작성) 교육이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>이행·운영</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
           <t>검수·인수 문서</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>미정</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I37" s="7" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>FVT 승인 연계</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>REQ→기능→메뉴→화면→컴포넌트→DB, 커버리지 178/178</t>
+          <t>REQ→기능→메뉴→화면→컴포넌트→DB, 커버리지 179/179</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>14모듈 178기능 — v0.3 보강 예정(Constant·AR 등)</t>
+          <t>14모듈 179기능(SYS-021 i18n) — v0.3</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>97메뉴, PPT 3차 전수 대조</t>
+          <t>98메뉴 — PPT 3차 전수 대조+다국어 관리</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>39컴포넌트·API 106·구축 상태 반영</t>
+          <t>39컴포넌트·API 108·구축 상태 반영</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>53테이블 455컬럼 — v0.4 런타임 경로 리뷰까지 반영</t>
+          <t>54테이블 462컬럼 — v0.5 i18n(sys_translation, 미결정 #7 해소)</t>
         </is>
       </c>
     </row>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>OpenAPI 3.1 자동 생성(105 op·52 스키마)+외부 연계 8종</t>
+          <t>OpenAPI 3.1 자동 생성(107 op)+Accept-Language·외부 연계 8종</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>기능 178·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
+          <t>기능 179·비기능 22 자동 생성 — 판정 기입 후 버전 고정</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>v0.1</t>
+          <t>v0.2</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-07 (v0.2 갱신 2026-07-11 — 착수 문서 3종 완료 반영)</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>37종 — 예정 16 · 완료 19 · 진행 2</t>
+          <t>37종 — 예정 13 · 완료 22 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 착수 문서(수행계획·위험대장·보안계획) ② 배치·보고서양식 정의서 ③ 운영·사용자 매뉴얼(안정화 단계)</t>
+          <t>① 배치·보고서양식 정의서 ② 운영·사용자 매뉴얼(안정화 단계) ③ 현행분석·제안서(고객사·사업 조건 확정 후) — 착수 3종은 v0.2 완료</t>
         </is>
       </c>
     </row>
@@ -804,17 +804,17 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_사업수행계획서.md</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>착수 시 — 범위·조직·일정·보고 체계</t>
+          <t>범위·조직·일정·관리 체계 — 계약 확정(시작일·인력·협의 4건) 시 v1.0 승격</t>
         </is>
       </c>
     </row>
@@ -897,14 +897,14 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_위험관리대장.xlsx</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>미결정사항(DB정의서 §12 등)이 초기 위험 항목</t>
+          <t>초기 위험 14건(협의 4건·미결정·이행·일정) — make_risk_xlsx.py 재생성, 주간 갱신</t>
         </is>
       </c>
     </row>
@@ -939,17 +939,17 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_보안관리계획서.md</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Management Grade·개인정보·서버 보안 포함</t>
+          <t>REQ-N-006~010·022 기준선 + Grade·개인정보·서버 보안 — 보안 솔루션 범위 협의 후 v0.2</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>37종 — 예정 13 · 완료 22 · 진행 2</t>
+          <t>37종 — 예정 11 · 완료 24 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 배치·보고서양식 정의서 ② 운영·사용자 매뉴얼(안정화 단계) ③ 현행분석·제안서(고객사·사업 조건 확정 후) — 착수 3종은 v0.2 완료</t>
+          <t>① 운영·사용자 매뉴얼(안정화 단계) ② 현행분석·제안서(고객사·사업 조건 확정 후) ③ 구현·시험 문서(테스트 계획·결함대장) — 착수 3종·배치/보고서양식은 완료</t>
         </is>
       </c>
     </row>
@@ -1794,17 +1794,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.2</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1814,12 +1814,12 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_배치보고서양식정의서.md (A부)</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>EDIM Run·AI 파이프라인·재고단가 산출 등 비동기 잡</t>
+          <t>공통 규약 + 업무 잡 JOB-01~08(Run·AI·재고단가·MRP·정산) + 운영 배치 BAT-01~06 — 통합본</t>
         </is>
       </c>
     </row>
@@ -1839,17 +1839,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.2</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1859,12 +1859,12 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_배치보고서양식정의서.md (B부)</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Print Form(견적서·PCR·작업지시서·검사성적서 등) — S-3-4</t>
+          <t>렌더 통제(Print Set-up·Grade·워터마크)·RPT-01~07 구현·FORM-01~04(고객 양식 확정 대기) — 통합본</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>37종 — 예정 11 · 완료 24 · 진행 2</t>
+          <t>37종 — 예정 9 · 완료 26 · 진행 2</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 운영·사용자 매뉴얼(안정화 단계) ② 현행분석·제안서(고객사·사업 조건 확정 후) ③ 구현·시험 문서(테스트 계획·결함대장) — 착수 3종·배치/보고서양식은 완료</t>
+          <t>① 설치·배포 매뉴얼(Self-managed 정식본) ② 현행분석·제안서(고객사·사업 조건 확정 후) ③ 구현·시험 문서(테스트 계획·결함대장) — 착수 3종·배치/보고서양식·매뉴얼 2종 완료</t>
         </is>
       </c>
     </row>
@@ -2199,17 +2199,17 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2219,12 +2219,12 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_관리자가이드.md</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>백업·모니터링·테넌트 관리·장애 대응</t>
+          <t>계정·권한/문서 통제/승인 운영/서버 운영/장애 대응 — 개발 서버 기준, 운영 이관 시 확장</t>
         </is>
       </c>
     </row>
@@ -2244,17 +2244,17 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>문서</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>예정</t>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>docs/EDIM_사용자가이드.md</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>역할별(Set-up/일반/관리자) — 화면설계서 기반</t>
+          <t>공통 조작(F-Key·탭·검색)+모듈별(CPQ/PLM/Code/ERP/Toolbox/공통)+FAQ — GENERAL·SETUP 대상</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>37종 — 예정 9 · 완료 26 · 진행 2</t>
+          <t>37종 — 예정 9 · 완료 27 · 진행 1</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>① 설치·배포 매뉴얼(Self-managed 정식본) ② 현행분석·제안서(고객사·사업 조건 확정 후) ③ 구현·시험 문서(테스트 계획·결함대장) — 착수 3종·배치/보고서양식·매뉴얼 2종 완료</t>
+          <t>① 현행분석·제안서(고객사·사업 조건 확정 후) ② 구현·시험 문서(테스트 계획·결함대장 — 본사업 병행) ③ 교육·검수 문서(안정화 단계) — 협의 불요 문서는 전량 완료(2026-07-11)</t>
         </is>
       </c>
     </row>
@@ -2157,14 +2157,14 @@
           <t>MD</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>진행</t>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>완료</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>v0.1</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>컴포넌트정의서 §8 구축 현황 + 서버 구축 이력</t>
+          <t>docs/EDIM_설치배포매뉴얼.md</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>Self-managed 패키지용 정식 매뉴얼 필요</t>
+          <t>Self-managed 단일 서버 정식 절차(검증 구성 정본) + 검증 체크리스트 8·업그레이드/롤백·운영 확장(§8)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1889,12 +1889,12 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>backend/tests/ (pytest 63케이스)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>P1 개발과 병행</t>
+          <t>CI backend-unit 잡 자동 실행 — macro_engine 35 + design_rules 28. DB 불요</t>
         </is>
       </c>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tests/live_all.py (115 스위트)</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>E2E: 코드 등록→CPQ→Run→견적 (개요 §7 워크플로우 기반)</t>
+          <t>E2E 상시: 시연 8단계(live_demo_scenario)·코드→CPQ→Run→견적 전 구간. 매 배포 실행</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>예정</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>자동</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -2039,12 +2039,12 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>tests/load_baseline.py · docs/EDIM_Launch준비상태.xlsx</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>REQ-N-001~005 목표 검증 (산출물 1시간·BOM 30초 등)</t>
+          <t>BOM 전개 동시5·50회 실측 46.5req/s·p95 138ms (REQ-N BOM 30s 목표 대비 여유). 핵심쿼리 인덱스 백업 EXPLAIN 확인</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1904,12 +1904,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>backend/tests/ (pytest 63케이스)</t>
+          <t>backend/tests/ (pytest 174케이스)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>CI backend-unit 잡 자동 실행 — macro_engine 35 + design_rules 28. DB 불요</t>
+          <t>CI backend-unit 잡 자동 실행 — macro_engine 35 + design_rules 28 + macro_graph 12 + llm_parse 17 + password 21 + migration_chain 62 (DB 불요 정적 검사 포함)</t>
         </is>
       </c>
     </row>
@@ -1949,12 +1949,12 @@
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>tests/live_all.py (115 스위트)</t>
+          <t>tests/live_all.py (121 스위트 + 정적·라이브 게이트 10종)</t>
         </is>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>E2E 상시: 시연 8단계(live_demo_scenario)·코드→CPQ→Run→견적 전 구간. 매 배포 실행</t>
+          <t>E2E 상시: 시연 8단계(live_demo_scenario)·코드→CPQ→Run→견적 전 구간. 게이트 10종 = 테넌트스코프·커서재사용·승인동사·거버넌스·FK인덱스·실데이터잔재·i18n EN 62화면·a11y 이름 62화면·감사 커버리지·검증 코드 문법. 러너는 등록 대비 실행 수를 검사해 조용한 미실행을 실패로 처리(14.2)</t>
         </is>
       </c>
     </row>

--- a/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
+++ b/edim-ai-blueprint/docs/EDIM_산출물목록.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>MD+Excel</t>
+          <t>MD+Excel(자동)</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>v0.2</t>
+          <t>v0.3</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>docs/EDIM_DB_정의서.md / EDIM_DB정의서.xlsx</t>
+          <t>docs/EDIM_DB_정의서.md(설계) / EDIM_DB정의서.xlsx(생성) / ddl/schema_snapshot.json · column_descriptions.json</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>54테이블 462컬럼 — v0.5 i18n(sys_translation, 미결정 #7 해소)</t>
+          <t>**실 스키마에서 생성**(tools/gen_db_dict.py) — 107테이블 1,181컬럼 351제약. 종전 v0.2 는 설계 초안 기준 54테이블뿐이었고 나머지는 행조차 없었다(18.2). 드리프트 게이트 tests/check_db_dict.py — 문서=생성기 + 스냅샷=실 스키마 이중 검사. 설명 미기재 테이블 53·컬럼 947 은 '미기재' 시트에 수치로 드러낸다</t>
         </is>
       </c>
     </row>
@@ -1904,12 +1904,12 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>backend/tests/ (pytest 174케이스)</t>
+          <t>backend/tests/ (pytest 187케이스)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>CI backend-unit 잡 자동 실행 — macro_engine 35 + design_rules 28 + macro_graph 12 + llm_parse 17 + password 21 + migration_chain 62 (DB 불요 정적 검사 포함)</t>
+          <t>CI backend-unit 잡 자동 실행 — macro_engine 35 · migration_chain 66 · design_rules 28 · password 21 · llm_parse 17 · macro_graph 12 · db_api 8 (2026-07-26 실측. 종전 기재 174 는 낡은 값이었다)</t>
         </is>
       </c>
     </row>
